--- a/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
+++ b/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-05T10:09:20-03:00</t>
+    <t>2026-06-16T17:47:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
+++ b/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
+++ b/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
+++ b/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
+++ b/docs/StructureDefinition-BRRoupasUsadasMedicao.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
